--- a/INPUT/CxC al 25-3-2026.xlsx
+++ b/INPUT/CxC al 25-3-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Documents\rodri\xio\xio\Veritrade_Dashboard\INPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A236049D-BF27-4540-A4B7-1F251A1AD43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0102BF8F-B6EE-4683-877A-3605A7F13F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,9 +23,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId5"/>
-    <pivotCache cacheId="11" r:id="rId6"/>
-    <pivotCache cacheId="12" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5663,7 +5663,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{555B5BC3-55CB-4710-AA0F-AFDAF83F1941}" name="TablaDinámica2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{555B5BC3-55CB-4710-AA0F-AFDAF83F1941}" name="TablaDinámica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:O19" firstHeaderRow="1" firstDataRow="4" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
@@ -6003,7 +6003,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD10559E-A6E4-491D-BF55-A8D147B7C22E}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD10559E-A6E4-491D-BF55-A8D147B7C22E}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -6368,7 +6368,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{12D76F04-516E-4F5F-93F1-491515CEABED}" name="TablaDinámica3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{12D76F04-516E-4F5F-93F1-491515CEABED}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F4:I7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -6565,7 +6565,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFD24885-0E38-462C-9A45-60766236540C}" name="TablaDinámica2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFD24885-0E38-462C-9A45-60766236540C}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:D37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -6852,7 +6852,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78C9CAC0-25A5-4DBD-9091-74FD25655C81}" name="TablaDinámica4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78C9CAC0-25A5-4DBD-9091-74FD25655C81}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F18:I21" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -10421,7 +10421,10 @@
         <f t="shared" si="8"/>
         <v>20964</v>
       </c>
-      <c r="Q31" s="17"/>
+      <c r="Q31" s="17">
+        <f t="shared" ref="Q31" ca="1" si="9">TODAY()-F31</f>
+        <v>205</v>
+      </c>
       <c r="R31" s="18"/>
     </row>
     <row r="32" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
@@ -10463,7 +10466,7 @@
         <v>46087</v>
       </c>
       <c r="M32" s="21">
-        <f t="shared" ref="M32:M34" ca="1" si="9">N32-TODAY()</f>
+        <f t="shared" ref="M32:M34" ca="1" si="10">N32-TODAY()</f>
         <v>-9</v>
       </c>
       <c r="N32" s="12">
@@ -10477,7 +10480,7 @@
         <v>140400</v>
       </c>
       <c r="Q32" s="17">
-        <f t="shared" ref="Q32:Q34" ca="1" si="10">TODAY()-F32</f>
+        <f t="shared" ref="Q32:Q34" ca="1" si="11">TODAY()-F32</f>
         <v>68</v>
       </c>
       <c r="R32" s="18" t="s">
@@ -10523,7 +10526,7 @@
         <v>46099</v>
       </c>
       <c r="M33" s="21">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="10"/>
         <v>-9</v>
       </c>
       <c r="N33" s="12">
@@ -10537,7 +10540,7 @@
         <v>77585</v>
       </c>
       <c r="Q33" s="17">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="11"/>
         <v>56</v>
       </c>
       <c r="R33" s="18" t="s">
@@ -10583,14 +10586,14 @@
         <v>46126</v>
       </c>
       <c r="M34" s="21">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="10"/>
         <v>16</v>
       </c>
       <c r="N34" s="12">
         <v>46126</v>
       </c>
       <c r="O34" s="22">
-        <f t="shared" ref="O34" si="11">H34+45</f>
+        <f t="shared" ref="O34" si="12">H34+45</f>
         <v>46126</v>
       </c>
       <c r="P34" s="23">
@@ -10598,7 +10601,7 @@
         <v>53862.5</v>
       </c>
       <c r="Q34" s="17">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="11"/>
         <v>29</v>
       </c>
       <c r="R34" s="18" t="s">
@@ -10642,11 +10645,11 @@
       <c r="L35" s="12"/>
       <c r="M35" s="12"/>
       <c r="O35" s="12">
-        <f t="shared" ref="O35:O42" si="12">H35</f>
+        <f t="shared" ref="O35:O42" si="13">H35</f>
         <v>46043</v>
       </c>
       <c r="P35" s="13">
-        <f t="shared" ref="P35:P42" si="13">I35/3.477</f>
+        <f t="shared" ref="P35:P42" si="14">I35/3.477</f>
         <v>66.586137474834629</v>
       </c>
     </row>
@@ -10687,11 +10690,11 @@
       <c r="L36" s="12"/>
       <c r="M36" s="12"/>
       <c r="O36" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46043</v>
       </c>
       <c r="P36" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.7874604544147257</v>
       </c>
     </row>
@@ -10732,11 +10735,11 @@
       <c r="L37" s="12"/>
       <c r="M37" s="12"/>
       <c r="O37" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46058</v>
       </c>
       <c r="P37" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>72.217428817946512</v>
       </c>
     </row>
@@ -10777,11 +10780,11 @@
       <c r="L38" s="12"/>
       <c r="M38" s="12"/>
       <c r="O38" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46058</v>
       </c>
       <c r="P38" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.574920908829451</v>
       </c>
     </row>
@@ -10822,11 +10825,11 @@
       <c r="L39" s="12"/>
       <c r="M39" s="12"/>
       <c r="O39" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46065</v>
       </c>
       <c r="P39" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>96.042565429968363</v>
       </c>
     </row>
@@ -10867,11 +10870,11 @@
       <c r="L40" s="12"/>
       <c r="M40" s="12"/>
       <c r="O40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46065</v>
       </c>
       <c r="P40" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.574920908829451</v>
       </c>
     </row>
@@ -10912,11 +10915,11 @@
       <c r="L41" s="12"/>
       <c r="M41" s="12"/>
       <c r="O41" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46109</v>
       </c>
       <c r="P41" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>105.57089444923785</v>
       </c>
     </row>
@@ -10957,11 +10960,11 @@
       <c r="L42" s="12"/>
       <c r="M42" s="12"/>
       <c r="O42" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46109</v>
       </c>
       <c r="P42" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>39.027897612884672</v>
       </c>
     </row>
@@ -11008,11 +11011,11 @@
         <v>46141</v>
       </c>
       <c r="P43" s="23">
-        <f t="shared" ref="P43:P44" si="14">I43</f>
+        <f t="shared" ref="P43:P44" si="15">I43</f>
         <v>147743.07</v>
       </c>
       <c r="Q43" s="17">
-        <f t="shared" ref="Q43:Q44" ca="1" si="15">TODAY()-F43</f>
+        <f t="shared" ref="Q43:Q44" ca="1" si="16">TODAY()-F43</f>
         <v>14</v>
       </c>
       <c r="R43" s="18" t="s">
@@ -11057,11 +11060,11 @@
       <c r="M44" s="21"/>
       <c r="O44" s="12"/>
       <c r="P44" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-7410</v>
       </c>
       <c r="Q44" s="17">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v>12</v>
       </c>
       <c r="R44" s="18" t="s">
@@ -11105,11 +11108,11 @@
       <c r="L45" s="12"/>
       <c r="M45" s="12"/>
       <c r="O45" s="12">
-        <f t="shared" ref="O45:O48" si="16">H45</f>
+        <f t="shared" ref="O45:O48" si="17">H45</f>
         <v>45971</v>
       </c>
       <c r="P45" s="13">
-        <f t="shared" ref="P45:P48" si="17">I45/3.477</f>
+        <f t="shared" ref="P45:P48" si="18">I45/3.477</f>
         <v>403.58354903652577</v>
       </c>
     </row>
@@ -11150,11 +11153,11 @@
       <c r="L46" s="12"/>
       <c r="M46" s="12"/>
       <c r="O46" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>45971</v>
       </c>
       <c r="P46" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>40.72476272648835</v>
       </c>
     </row>
@@ -11195,11 +11198,11 @@
       <c r="L47" s="12"/>
       <c r="M47" s="12"/>
       <c r="O47" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>45974</v>
       </c>
       <c r="P47" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>343.17515099223471</v>
       </c>
     </row>
@@ -11240,11 +11243,11 @@
       <c r="L48" s="12"/>
       <c r="M48" s="12"/>
       <c r="O48" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>45974</v>
       </c>
       <c r="P48" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>30.543572044866266</v>
       </c>
     </row>
@@ -11287,7 +11290,7 @@
         <v>46113</v>
       </c>
       <c r="M49" s="21">
-        <f t="shared" ref="M49:M52" ca="1" si="18">N49-TODAY()</f>
+        <f t="shared" ref="M49:M52" ca="1" si="19">N49-TODAY()</f>
         <v>1</v>
       </c>
       <c r="N49" s="12">
@@ -11297,11 +11300,11 @@
         <v>46111</v>
       </c>
       <c r="P49" s="23">
-        <f t="shared" ref="P49:P52" si="19">I49</f>
+        <f t="shared" ref="P49:P52" si="20">I49</f>
         <v>12898</v>
       </c>
       <c r="Q49" s="17">
-        <f t="shared" ref="Q49:Q52" ca="1" si="20">TODAY()-F49</f>
+        <f t="shared" ref="Q49:Q52" ca="1" si="21">TODAY()-F49</f>
         <v>42</v>
       </c>
       <c r="R49" s="18" t="s">
@@ -11347,7 +11350,7 @@
         <v>46114</v>
       </c>
       <c r="M50" s="21">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v>1</v>
       </c>
       <c r="N50" s="12">
@@ -11357,11 +11360,11 @@
         <v>46111</v>
       </c>
       <c r="P50" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>30190</v>
       </c>
       <c r="Q50" s="17">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v>41</v>
       </c>
       <c r="R50" s="18" t="s">
@@ -11407,7 +11410,7 @@
         <v>46133</v>
       </c>
       <c r="M51" s="21">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v>23</v>
       </c>
       <c r="N51" s="12">
@@ -11417,11 +11420,11 @@
         <v>46133</v>
       </c>
       <c r="P51" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>67600</v>
       </c>
       <c r="Q51" s="17">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v>22</v>
       </c>
       <c r="R51" s="18" t="s">
@@ -11467,7 +11470,7 @@
         <v>46133</v>
       </c>
       <c r="M52" s="21">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v>23</v>
       </c>
       <c r="N52" s="12">
@@ -11477,11 +11480,11 @@
         <v>46133</v>
       </c>
       <c r="P52" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>67600</v>
       </c>
       <c r="Q52" s="17">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v>22</v>
       </c>
       <c r="R52" s="18" t="s">
@@ -11570,11 +11573,11 @@
       <c r="L54" s="12"/>
       <c r="M54" s="12"/>
       <c r="O54" s="12">
-        <f t="shared" ref="O54:O57" si="21">H54</f>
+        <f t="shared" ref="O54:O57" si="22">H54</f>
         <v>45972</v>
       </c>
       <c r="P54" s="13">
-        <f t="shared" ref="P54:P57" si="22">I54/3.477</f>
+        <f t="shared" ref="P54:P57" si="23">I54/3.477</f>
         <v>2041.4092608570606</v>
       </c>
     </row>
@@ -11615,11 +11618,11 @@
       <c r="L55" s="12"/>
       <c r="M55" s="12"/>
       <c r="O55" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>46060</v>
       </c>
       <c r="P55" s="13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1151.4121368996261</v>
       </c>
     </row>
@@ -11660,11 +11663,11 @@
       <c r="L56" s="12"/>
       <c r="M56" s="12"/>
       <c r="O56" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>46091</v>
       </c>
       <c r="P56" s="13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1425.3666954270923</v>
       </c>
     </row>
@@ -11705,11 +11708,11 @@
       <c r="L57" s="12"/>
       <c r="M57" s="12"/>
       <c r="O57" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>46091</v>
       </c>
       <c r="P57" s="13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1425.3666954270923</v>
       </c>
     </row>
@@ -11752,7 +11755,7 @@
         <v>46133</v>
       </c>
       <c r="M58" s="21">
-        <f t="shared" ref="M58" ca="1" si="23">N58-TODAY()</f>
+        <f t="shared" ref="M58" ca="1" si="24">N58-TODAY()</f>
         <v>23</v>
       </c>
       <c r="N58" s="12">
@@ -11762,11 +11765,11 @@
         <v>46133</v>
       </c>
       <c r="P58" s="23">
-        <f t="shared" ref="P58:P60" si="24">I58</f>
+        <f t="shared" ref="P58:P60" si="25">I58</f>
         <v>156680</v>
       </c>
       <c r="Q58" s="17">
-        <f t="shared" ref="Q58:Q60" ca="1" si="25">TODAY()-F58</f>
+        <f t="shared" ref="Q58:Q60" ca="1" si="26">TODAY()-F58</f>
         <v>22</v>
       </c>
       <c r="R58" s="18" t="s">
@@ -11817,11 +11820,11 @@
         <v>46144</v>
       </c>
       <c r="P59" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>125360</v>
       </c>
       <c r="Q59" s="17">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="26"/>
         <v>11</v>
       </c>
       <c r="R59" s="18" t="s">
@@ -11872,11 +11875,11 @@
         <v>46144</v>
       </c>
       <c r="P60" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>31275</v>
       </c>
       <c r="Q60" s="17">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="26"/>
         <v>11</v>
       </c>
       <c r="R60" s="18" t="s">
@@ -12026,11 +12029,11 @@
       <c r="L63" s="12"/>
       <c r="M63" s="12"/>
       <c r="O63" s="12">
-        <f t="shared" ref="O63:O66" si="26">H63</f>
+        <f t="shared" ref="O63:O66" si="27">H63</f>
         <v>46108</v>
       </c>
       <c r="P63" s="13">
-        <f t="shared" ref="P63:P66" si="27">I63/3.477</f>
+        <f t="shared" ref="P63:P66" si="28">I63/3.477</f>
         <v>169.68651136036814</v>
       </c>
     </row>
@@ -12071,11 +12074,11 @@
       <c r="L64" s="12"/>
       <c r="M64" s="12"/>
       <c r="O64" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>46087</v>
       </c>
       <c r="P64" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>191.40638481449525</v>
       </c>
     </row>
@@ -12116,11 +12119,11 @@
       <c r="L65" s="12"/>
       <c r="M65" s="12"/>
       <c r="O65" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>46087</v>
       </c>
       <c r="P65" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>35.634167385677308</v>
       </c>
     </row>
@@ -12161,11 +12164,11 @@
       <c r="L66" s="12"/>
       <c r="M66" s="12"/>
       <c r="O66" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>45942</v>
       </c>
       <c r="P66" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>16.28990509059534</v>
       </c>
     </row>
@@ -12208,7 +12211,7 @@
       <c r="N67" s="12"/>
       <c r="O67" s="12"/>
       <c r="P67" s="8">
-        <f t="shared" ref="P67:P74" si="28">I67</f>
+        <f t="shared" ref="P67:P74" si="29">I67</f>
         <v>-376.07</v>
       </c>
       <c r="Q67" s="17"/>
@@ -12249,11 +12252,11 @@
         <v>198</v>
       </c>
       <c r="L68" s="12">
-        <f t="shared" ref="L68:L74" si="29">F68+45</f>
+        <f t="shared" ref="L68:L74" si="30">F68+45</f>
         <v>46111</v>
       </c>
       <c r="M68" s="21">
-        <f t="shared" ref="M68:M73" ca="1" si="30">N68-TODAY()</f>
+        <f t="shared" ref="M68:M73" ca="1" si="31">N68-TODAY()</f>
         <v>-9</v>
       </c>
       <c r="N68" s="12">
@@ -12263,11 +12266,11 @@
         <v>46105</v>
       </c>
       <c r="P68" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>44456</v>
       </c>
       <c r="Q68" s="17">
-        <f t="shared" ref="Q68:Q74" ca="1" si="31">TODAY()-F68</f>
+        <f t="shared" ref="Q68:Q74" ca="1" si="32">TODAY()-F68</f>
         <v>44</v>
       </c>
       <c r="R68" s="18" t="s">
@@ -12309,11 +12312,11 @@
         <v>198</v>
       </c>
       <c r="L69" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>46120</v>
       </c>
       <c r="M69" s="21">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>10</v>
       </c>
       <c r="N69" s="12">
@@ -12323,11 +12326,11 @@
         <v>46105</v>
       </c>
       <c r="P69" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>48000</v>
       </c>
       <c r="Q69" s="17">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>35</v>
       </c>
       <c r="R69" s="18" t="s">
@@ -12369,11 +12372,11 @@
         <v>198</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>46133</v>
       </c>
       <c r="M70" s="21">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>23</v>
       </c>
       <c r="N70" s="12">
@@ -12383,11 +12386,11 @@
         <v>46133</v>
       </c>
       <c r="P70" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>39610</v>
       </c>
       <c r="Q70" s="17">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>22</v>
       </c>
       <c r="R70" s="18" t="s">
@@ -12429,11 +12432,11 @@
         <v>198</v>
       </c>
       <c r="L71" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>46133</v>
       </c>
       <c r="M71" s="21">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>23</v>
       </c>
       <c r="N71" s="12">
@@ -12443,11 +12446,11 @@
         <v>46133</v>
       </c>
       <c r="P71" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>94640</v>
       </c>
       <c r="Q71" s="17">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>22</v>
       </c>
       <c r="R71" s="18" t="s">
@@ -12489,11 +12492,11 @@
         <v>198</v>
       </c>
       <c r="L72" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>46136</v>
       </c>
       <c r="M72" s="21">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>26</v>
       </c>
       <c r="N72" s="12">
@@ -12503,11 +12506,11 @@
         <v>46136</v>
       </c>
       <c r="P72" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>76800</v>
       </c>
       <c r="Q72" s="17">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>19</v>
       </c>
       <c r="R72" s="18" t="s">
@@ -12549,11 +12552,11 @@
         <v>198</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>46136</v>
       </c>
       <c r="M73" s="21">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>26</v>
       </c>
       <c r="N73" s="12">
@@ -12563,11 +12566,11 @@
         <v>46136</v>
       </c>
       <c r="P73" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>186880</v>
       </c>
       <c r="Q73" s="17">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>19</v>
       </c>
       <c r="R73" s="18" t="s">
@@ -12609,7 +12612,7 @@
         <v>198</v>
       </c>
       <c r="L74" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>46144</v>
       </c>
       <c r="M74" s="21"/>
@@ -12619,11 +12622,11 @@
         <v>46144</v>
       </c>
       <c r="P74" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216000</v>
       </c>
       <c r="Q74" s="17">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>11</v>
       </c>
       <c r="R74" s="18" t="s">
